--- a/artfynd/A 45595-2019 artfynd.xlsx
+++ b/artfynd/A 45595-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126413248</v>
       </c>
       <c r="B2" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126413216</v>
       </c>
       <c r="B3" t="n">
-        <v>98272</v>
+        <v>98281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
